--- a/QLDA.WebApi/PrintTemplates/Import_GoiThau.xlsx
+++ b/QLDA.WebApi/PrintTemplates/Import_GoiThau.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tranp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SER\QLDA.WebApi\PrintTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0998A20D-D833-42BE-B555-0205721EE6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A64EC6-D2BA-448E-A078-91E31C164F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tài liệu" sheetId="4" r:id="rId1"/>
@@ -26,42 +26,84 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
-  <si>
-    <t>STT</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+  <si>
+    <t>Thời gian thực hiện gói thầu</t>
+  </si>
+  <si>
+    <t>Phương thức lựa chọn nhà thầu</t>
+  </si>
+  <si>
+    <t>Nhập số tiền (đồng)</t>
   </si>
   <si>
     <t>Giá gói thầu</t>
   </si>
   <si>
+    <t>Tóm tắt công việc chính</t>
+  </si>
+  <si>
+    <t>Loại hợp đồng</t>
+  </si>
+  <si>
+    <t>Nhập ngày (dd/MM/yyyy)</t>
+  </si>
+  <si>
+    <t>Mô tả ngắn</t>
+  </si>
+  <si>
+    <t>Nhập tên gói thầu</t>
+  </si>
+  <si>
+    <t>MẪU IMPORT GÓI THẦU</t>
+  </si>
+  <si>
+    <t>Thời gian bắt đầu tổ chức lựa chọn nhà thầu</t>
+  </si>
+  <si>
+    <t>Chọn từ danh sách</t>
+  </si>
+  <si>
     <t>Hình thức lựa chọn nhà thầu</t>
   </si>
   <si>
-    <t>Phương thức lựa chọn nhà thầu</t>
-  </si>
-  <si>
-    <t>Thời gian bắt đầu tổ chức lựa chọn nhà thầu</t>
-  </si>
-  <si>
-    <t>Loại hợp đồng</t>
-  </si>
-  <si>
-    <t>Tóm tắt công việc chính</t>
+    <t>$cbo1</t>
+  </si>
+  <si>
+    <t>$cbo2</t>
+  </si>
+  <si>
+    <t>$cbo3</t>
+  </si>
+  <si>
+    <t>Hình thức</t>
+  </si>
+  <si>
+    <t>$cbo4</t>
+  </si>
+  <si>
+    <t>Nguồn vốn</t>
+  </si>
+  <si>
+    <t>$Kế hoạch</t>
+  </si>
+  <si>
+    <t>Phương thức</t>
+  </si>
+  <si>
+    <t>$cbo5</t>
+  </si>
+  <si>
+    <t>Thời gian tổ chức lựa chọn nhà thầu</t>
+  </si>
+  <si>
+    <t>Nhập số ngày</t>
   </si>
   <si>
     <t>Tùy chọn mua thêm</t>
   </si>
   <si>
-    <t>Nội dung</t>
-  </si>
-  <si>
-    <t>Thời gian tổ chức lựa chọn nhà thầu</t>
-  </si>
-  <si>
-    <t>Thời gian thực hiện gói thầu</t>
-  </si>
-  <si>
-    <t/>
+    <t>có / không</t>
   </si>
   <si>
     <t>Kế hoạch lựa chọn nhà thầu *</t>
@@ -71,125 +113,61 @@
   </si>
   <si>
     <t>Nguồn vốn*</t>
-  </si>
-  <si>
-    <t>$cbo1</t>
-  </si>
-  <si>
-    <t>$cbo2</t>
-  </si>
-  <si>
-    <t>$cbo3</t>
-  </si>
-  <si>
-    <t>Hình thức</t>
-  </si>
-  <si>
-    <t>$cbo4</t>
-  </si>
-  <si>
-    <t>Nguồn vốn</t>
-  </si>
-  <si>
-    <t>$Kế hoạch</t>
-  </si>
-  <si>
-    <t>Phương thức</t>
-  </si>
-  <si>
-    <t>$cbo5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="163"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <scheme val="major"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri Light"/>
       <family val="1"/>
       <scheme val="major"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Calibri Light"/>
       <family val="1"/>
+      <scheme val="major"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -197,104 +175,34 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Good" xfId="1" builtinId="26"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -307,6 +215,40 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="GoiThauImport" displayName="GoiThauImport" ref="A4:L6" totalsRowShown="0">
+  <autoFilter ref="A4:L6" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Kế hoạch lựa chọn nhà thầu *"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Tên gói thầu *"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Tóm tắt công việc chính"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Giá gói thầu"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nguồn vốn*"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Hình thức lựa chọn nhà thầu"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Phương thức lựa chọn nhà thầu"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Thời gian tổ chức lựa chọn nhà thầu"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Thời gian bắt đầu tổ chức lựa chọn nhà thầu"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Loại hợp đồng"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Thời gian thực hiện gói thầu"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Tùy chọn mua thêm"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -572,155 +514,171 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE6D5104-4496-4E0E-921E-5FD597594020}">
-  <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="26.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="40.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="27.125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="19.5" style="2" customWidth="1"/>
-    <col min="14" max="15" width="12.875" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="25.109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="25.44140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18" style="3" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="26.77734375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="29.21875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="33" style="3" customWidth="1"/>
+    <col min="9" max="9" width="39.6640625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="26.44140625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="19.6640625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="19.44140625" style="3" customWidth="1"/>
+    <col min="14" max="15" width="12.88671875" style="3" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:16" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="L4" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="12" t="s">
+      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="13"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <v>1</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="F6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="6" t="s">
+      <c r="G6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <v>2</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="7" t="s">
-        <v>11</v>
+      <c r="J6" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="K2:K3"/>
@@ -728,60 +686,59 @@
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="L2:L3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BC5DD92-66CA-42BB-B5AC-A68834D38DC2}">
   <dimension ref="C3:O4"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="9" style="16"/>
+    <col min="1" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:15" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="16" t="s">
+    <row r="3" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="O4" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="O3" s="16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="3:15" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4" s="16" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>